--- a/data/dividends_info_20260316.xlsx
+++ b/data/dividends_info_20260316.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50.29999923706055</v>
+        <v>50.84999847412109</v>
       </c>
       <c r="I2" t="n">
-        <v>1.391650120511825</v>
+        <v>1.376597878083022</v>
       </c>
       <c r="J2" t="n">
         <v>343</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5.489999771118164</v>
+        <v>5.309999942779541</v>
       </c>
       <c r="I3" t="n">
-        <v>3.64298740142325</v>
+        <v>3.766478383337029</v>
       </c>
       <c r="J3" t="n">
         <v>245</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>17.79999923706055</v>
+        <v>17.89999961853027</v>
       </c>
       <c r="I4" t="n">
-        <v>2.112359641101265</v>
+        <v>2.100558703983215</v>
       </c>
       <c r="J4" t="n">
         <v>126</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24.18000030517578</v>
+        <v>24.55999946594238</v>
       </c>
       <c r="I5" t="n">
-        <v>3.928866782506411</v>
+        <v>3.868078260007193</v>
       </c>
       <c r="J5" t="n">
         <v>98</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>22.04999923706055</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8843537720956184</v>
+        <v>0.911214969514062</v>
       </c>
       <c r="J6" t="n">
         <v>98</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>64.08000183105469</v>
+        <v>63.79999923706055</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9831460393228127</v>
+        <v>0.9874608268553735</v>
       </c>
       <c r="J7" t="n">
         <v>98</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.18000030517578</v>
+        <v>21.45000076293945</v>
       </c>
       <c r="I8" t="n">
-        <v>4.013219961060551</v>
+        <v>3.962703821757432</v>
       </c>
       <c r="J8" t="n">
         <v>98</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.613999843597412</v>
+        <v>6.51200008392334</v>
       </c>
       <c r="I9" t="n">
-        <v>2.74115519031203</v>
+        <v>2.784090873210963</v>
       </c>
       <c r="J9" t="n">
         <v>98</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.878000020980835</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="I10" t="n">
-        <v>3.416856410377562</v>
+        <v>3.614457904003342</v>
       </c>
       <c r="J10" t="n">
         <v>77</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.52000045776367</v>
+        <v>9.017999649047852</v>
       </c>
       <c r="I11" t="n">
-        <v>2.756653872443346</v>
+        <v>3.215790766088786</v>
       </c>
       <c r="J11" t="n">
         <v>63</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>34.20999908447266</v>
+        <v>34.56999969482422</v>
       </c>
       <c r="I12" t="n">
-        <v>4.793920034754892</v>
+        <v>4.743997727733676</v>
       </c>
       <c r="J12" t="n">
         <v>63</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>32.13999938964844</v>
+        <v>32.2599983215332</v>
       </c>
       <c r="I13" t="n">
-        <v>6.222775475982599</v>
+        <v>6.199628344881288</v>
       </c>
       <c r="J13" t="n">
         <v>63</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3.865999937057495</v>
+        <v>3.726000070571899</v>
       </c>
       <c r="I14" t="n">
-        <v>2.58665291329809</v>
+        <v>2.683843212720367</v>
       </c>
       <c r="J14" t="n">
         <v>63</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>36.5</v>
+        <v>37.95000076293945</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4067397260273973</v>
+        <v>0.391198938116967</v>
       </c>
       <c r="J15" t="n">
         <v>63</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>22.3799991607666</v>
+        <v>22.1200008392334</v>
       </c>
       <c r="I16" t="n">
-        <v>4.11081338024718</v>
+        <v>4.159131849435698</v>
       </c>
       <c r="J16" t="n">
         <v>63</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>70.33999633789062</v>
+        <v>72.04000091552734</v>
       </c>
       <c r="I17" t="n">
-        <v>1.478532917465869</v>
+        <v>1.443642402530621</v>
       </c>
       <c r="J17" t="n">
         <v>63</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>50.29999923706055</v>
+        <v>50.84999847412109</v>
       </c>
       <c r="I18" t="n">
-        <v>4.373757521608592</v>
+        <v>4.326450473975212</v>
       </c>
       <c r="J18" t="n">
         <v>63</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7.13700008392334</v>
+        <v>7.072000026702881</v>
       </c>
       <c r="I19" t="n">
-        <v>12.04988076064646</v>
+        <v>12.16063343824605</v>
       </c>
       <c r="J19" t="n">
         <v>63</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>10.97000026702881</v>
+        <v>10.95499992370605</v>
       </c>
       <c r="I20" t="n">
-        <v>5.104831233989334</v>
+        <v>5.111821121862255</v>
       </c>
       <c r="J20" t="n">
         <v>63</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.809999942779541</v>
+        <v>1.804999947547913</v>
       </c>
       <c r="I21" t="n">
-        <v>2.209944821245335</v>
+        <v>2.216066546391865</v>
       </c>
       <c r="J21" t="n">
         <v>63</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>9.159999847412109</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I22" t="n">
-        <v>3.275109224862664</v>
+        <v>3.296703158506324</v>
       </c>
       <c r="J22" t="n">
         <v>63</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>61.90000152587891</v>
+        <v>62.5</v>
       </c>
       <c r="I23" t="n">
-        <v>3.327948221679386</v>
+        <v>3.296</v>
       </c>
       <c r="J23" t="n">
         <v>63</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>14.52000045776367</v>
+        <v>14.81999969482422</v>
       </c>
       <c r="I25" t="n">
-        <v>2.066115637342102</v>
+        <v>2.02429153966024</v>
       </c>
       <c r="J25" t="n">
         <v>63</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>34.56000137329102</v>
+        <v>32.31999969482422</v>
       </c>
       <c r="I26" t="n">
-        <v>2.459490643009363</v>
+        <v>2.629950519882339</v>
       </c>
       <c r="J26" t="n">
         <v>63</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.489999771118164</v>
+        <v>5.309999942779541</v>
       </c>
       <c r="I27" t="n">
-        <v>3.64298740142325</v>
+        <v>3.766478383337029</v>
       </c>
       <c r="J27" t="n">
         <v>63</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>21.78000068664551</v>
+        <v>21.52000045776367</v>
       </c>
       <c r="I28" t="n">
-        <v>4.591368082982449</v>
+        <v>4.646840049853412</v>
       </c>
       <c r="J28" t="n">
         <v>63</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4.099999904632568</v>
+        <v>4.179999828338623</v>
       </c>
       <c r="I29" t="n">
-        <v>5.243902560999395</v>
+        <v>5.143540881087874</v>
       </c>
       <c r="J29" t="n">
         <v>63</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>18.69499969482422</v>
+        <v>18.7549991607666</v>
       </c>
       <c r="I30" t="n">
-        <v>4.225728873473662</v>
+        <v>4.212210265797256</v>
       </c>
       <c r="J30" t="n">
         <v>63</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5.144000053405762</v>
+        <v>5.114999771118164</v>
       </c>
       <c r="I31" t="n">
-        <v>3.693623600843549</v>
+        <v>3.714565171103909</v>
       </c>
       <c r="J31" t="n">
         <v>63</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>10.19999980926514</v>
+        <v>10.3100004196167</v>
       </c>
       <c r="I32" t="n">
-        <v>4.235294196844927</v>
+        <v>4.190106521994309</v>
       </c>
       <c r="J32" t="n">
         <v>63</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>24.78000068664551</v>
+        <v>24.89999961853027</v>
       </c>
       <c r="I33" t="n">
-        <v>1.775625455237077</v>
+        <v>1.767068300163978</v>
       </c>
       <c r="J33" t="n">
         <v>63</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7.920000076293945</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="I34" t="n">
-        <v>5.934343377177466</v>
+        <v>7.142857225677318</v>
       </c>
       <c r="J34" t="n">
         <v>63</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>52.56000137329102</v>
+        <v>52.81999969482422</v>
       </c>
       <c r="I35" t="n">
-        <v>2.663622457040928</v>
+        <v>2.6505111853251</v>
       </c>
       <c r="J35" t="n">
         <v>63</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.983000040054321</v>
+        <v>2.78600001335144</v>
       </c>
       <c r="I36" t="n">
-        <v>10.05698947273688</v>
+        <v>10.76812629441134</v>
       </c>
       <c r="J36" t="n">
         <v>63</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>87.15000152587891</v>
+        <v>85.05000305175781</v>
       </c>
       <c r="I37" t="n">
-        <v>1.549053329160438</v>
+        <v>1.587301530346151</v>
       </c>
       <c r="J37" t="n">
         <v>63</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.36899995803833</v>
+        <v>3.381999969482422</v>
       </c>
       <c r="I38" t="n">
-        <v>5.046007780272756</v>
+        <v>5.026611517859258</v>
       </c>
       <c r="J38" t="n">
         <v>63</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4.53000020980835</v>
+        <v>4.690000057220459</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8830021666090007</v>
+        <v>0.8528784544131991</v>
       </c>
       <c r="J39" t="n">
         <v>63</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>29.64999961853027</v>
+        <v>29.25</v>
       </c>
       <c r="I40" t="n">
-        <v>3.541315391261539</v>
+        <v>3.58974358974359</v>
       </c>
       <c r="J40" t="n">
         <v>63</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>23.04000091552734</v>
+        <v>23.27000045776367</v>
       </c>
       <c r="I41" t="n">
-        <v>2.604166563186384</v>
+        <v>2.578427108710345</v>
       </c>
       <c r="J41" t="n">
         <v>63</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>30.79999923706055</v>
+        <v>31</v>
       </c>
       <c r="I42" t="n">
-        <v>1.136363664512229</v>
+        <v>1.129032258064516</v>
       </c>
       <c r="J42" t="n">
         <v>63</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2.476000070571899</v>
+        <v>2.426000118255615</v>
       </c>
       <c r="I43" t="n">
-        <v>3.271405399487362</v>
+        <v>3.338829185970611</v>
       </c>
       <c r="J43" t="n">
         <v>63</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>16.63999938964844</v>
+        <v>14.96000003814697</v>
       </c>
       <c r="I44" t="n">
-        <v>3.004807802523386</v>
+        <v>3.342245980782315</v>
       </c>
       <c r="J44" t="n">
         <v>56</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6.809999942779541</v>
+        <v>6.639999866485596</v>
       </c>
       <c r="I45" t="n">
-        <v>3.230543345793418</v>
+        <v>3.31325307866973</v>
       </c>
       <c r="J45" t="n">
         <v>56</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3.569999933242798</v>
+        <v>3.549999952316284</v>
       </c>
       <c r="I46" t="n">
-        <v>4.481792800894103</v>
+        <v>4.507042314059866</v>
       </c>
       <c r="J46" t="n">
         <v>49</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>18.3799991607666</v>
+        <v>18.45999908447266</v>
       </c>
       <c r="I47" t="n">
-        <v>3.318824961113642</v>
+        <v>3.304442200720866</v>
       </c>
       <c r="J47" t="n">
         <v>49</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>8.510000228881836</v>
+        <v>8.539999961853027</v>
       </c>
       <c r="I48" t="n">
-        <v>5.998824750526201</v>
+        <v>5.977751783142052</v>
       </c>
       <c r="J48" t="n">
         <v>49</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>6.949999809265137</v>
+        <v>7.46999979019165</v>
       </c>
       <c r="I49" t="n">
-        <v>3.884892192947393</v>
+        <v>3.614457932843836</v>
       </c>
       <c r="J49" t="n">
         <v>49</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>4.519999980926514</v>
+        <v>4.644999980926514</v>
       </c>
       <c r="I50" t="n">
-        <v>7.743362864533833</v>
+        <v>7.534983884546483</v>
       </c>
       <c r="J50" t="n">
         <v>49</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>18.79999923706055</v>
+        <v>18.5</v>
       </c>
       <c r="I51" t="n">
-        <v>3.989361864023487</v>
+        <v>4.054054054054054</v>
       </c>
       <c r="J51" t="n">
         <v>49</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>10.30000019073486</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="I52" t="n">
-        <v>4.174757204245461</v>
+        <v>4.257425581774359</v>
       </c>
       <c r="J52" t="n">
         <v>49</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>3.964999914169312</v>
+        <v>4.034999847412109</v>
       </c>
       <c r="I53" t="n">
-        <v>3.783102225651013</v>
+        <v>3.717472259539343</v>
       </c>
       <c r="J53" t="n">
         <v>49</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>11.47999954223633</v>
+        <v>11.53999996185303</v>
       </c>
       <c r="I54" t="n">
-        <v>1.717500068485116</v>
+        <v>1.708570196289149</v>
       </c>
       <c r="J54" t="n">
         <v>49</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>25.25</v>
+        <v>25</v>
       </c>
       <c r="I55" t="n">
-        <v>4.356435643564357</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>49</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>37.54999923706055</v>
+        <v>36.65000152587891</v>
       </c>
       <c r="I56" t="n">
-        <v>1.251664472834733</v>
+        <v>1.282401038013951</v>
       </c>
       <c r="J56" t="n">
         <v>49</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>10.25</v>
+        <v>10.39999961853027</v>
       </c>
       <c r="I57" t="n">
-        <v>3.707317073170731</v>
+        <v>3.653846287868437</v>
       </c>
       <c r="J57" t="n">
         <v>49</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>28</v>
+        <v>27.89999961853027</v>
       </c>
       <c r="I58" t="n">
-        <v>1.071428571428571</v>
+        <v>1.075268831906183</v>
       </c>
       <c r="J58" t="n">
         <v>49</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>5.78000020980835</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I59" t="n">
-        <v>2.768165989483679</v>
+        <v>2.739725955813527</v>
       </c>
       <c r="J59" t="n">
         <v>42</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>2.210000038146973</v>
+        <v>2.224999904632568</v>
       </c>
       <c r="I60" t="n">
-        <v>2.941176419820373</v>
+        <v>2.921348439820898</v>
       </c>
       <c r="J60" t="n">
         <v>42</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>7.159999847412109</v>
+        <v>7.150000095367432</v>
       </c>
       <c r="I61" t="n">
-        <v>3.491620186142313</v>
+        <v>3.496503449866776</v>
       </c>
       <c r="J61" t="n">
         <v>42</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>6.614999771118164</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="I62" t="n">
-        <v>7.558579248680498</v>
+        <v>7.598784282635446</v>
       </c>
       <c r="J62" t="n">
         <v>35</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>16.72999954223633</v>
+        <v>16.70999908447266</v>
       </c>
       <c r="I63" t="n">
-        <v>3.885236209116557</v>
+        <v>3.889886508755084</v>
       </c>
       <c r="J63" t="n">
         <v>35</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>11.43000030517578</v>
+        <v>11.48499965667725</v>
       </c>
       <c r="I64" t="n">
-        <v>4.724409322679326</v>
+        <v>4.70178507742532</v>
       </c>
       <c r="J64" t="n">
         <v>35</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>6.176000118255615</v>
+        <v>6.046000003814697</v>
       </c>
       <c r="I65" t="n">
-        <v>1.619170953452711</v>
+        <v>1.65398610547313</v>
       </c>
       <c r="J65" t="n">
         <v>35</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>9.100000381469727</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="I66" t="n">
-        <v>1.758241684536706</v>
+        <v>1.785714278111652</v>
       </c>
       <c r="J66" t="n">
         <v>35</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>289.2000122070312</v>
+        <v>288.6000061035156</v>
       </c>
       <c r="I67" t="n">
-        <v>1.249999947237938</v>
+        <v>1.252598726107915</v>
       </c>
       <c r="J67" t="n">
         <v>35</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>26.39999961853027</v>
+        <v>25.5</v>
       </c>
       <c r="I68" t="n">
-        <v>5.151515225952543</v>
+        <v>5.333333333333334</v>
       </c>
       <c r="J68" t="n">
         <v>35</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>12.86999988555908</v>
+        <v>12.88000011444092</v>
       </c>
       <c r="I69" t="n">
-        <v>4.545454585873038</v>
+        <v>4.541925425482755</v>
       </c>
       <c r="J69" t="n">
         <v>35</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>15.77000045776367</v>
+        <v>15.64000034332275</v>
       </c>
       <c r="I70" t="n">
-        <v>3.994926960765223</v>
+        <v>4.028132903903473</v>
       </c>
       <c r="J70" t="n">
         <v>35</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>98.41999816894531</v>
+        <v>98.01999664306641</v>
       </c>
       <c r="I71" t="n">
-        <v>0.914448299882187</v>
+        <v>0.9181799947181114</v>
       </c>
       <c r="J71" t="n">
         <v>35</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>63.5</v>
+        <v>63.84000015258789</v>
       </c>
       <c r="I72" t="n">
-        <v>2.70992125984252</v>
+        <v>2.695488715361859</v>
       </c>
       <c r="J72" t="n">
         <v>35</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>22.20000076293945</v>
+        <v>23.5</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6306306089579743</v>
+        <v>0.5957446808510638</v>
       </c>
       <c r="J73" t="n">
         <v>28</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.929999947547913</v>
+        <v>1.914999961853027</v>
       </c>
       <c r="I75" t="n">
-        <v>1.7616580789651</v>
+        <v>1.775456954427315</v>
       </c>
       <c r="J75" t="n">
         <v>14</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>22.35000038146973</v>
+        <v>22.53499984741211</v>
       </c>
       <c r="I76" t="n">
-        <v>1.163310942113293</v>
+        <v>1.153760824319944</v>
       </c>
       <c r="J76" t="n">
         <v>7</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>28.61499977111816</v>
+        <v>29.3799991607666</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3145203589721474</v>
+        <v>0.3063308460545635</v>
       </c>
       <c r="J77" t="n">
         <v>7</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>50.29999923706055</v>
+        <v>50.84999847412109</v>
       </c>
       <c r="I78" t="n">
-        <v>1.292246540475266</v>
+        <v>1.278269458219949</v>
       </c>
       <c r="J78" t="n">
         <v>-21</v>
@@ -4118,7 +4118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C335"/>
+  <dimension ref="A1:C305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4192,7 +4192,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4202,14 +4202,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4219,14 +4219,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4236,14 +4236,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4253,14 +4253,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4277,7 +4277,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4491,14 +4491,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4549,7 +4549,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4566,7 +4566,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4576,14 +4576,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4634,7 +4634,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4651,7 +4651,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4678,14 +4678,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4821,17 +4821,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4974,7 +4974,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4991,12 +4991,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5008,12 +5008,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5025,29 +5025,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5059,12 +5059,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5076,46 +5076,46 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5127,12 +5127,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5144,29 +5144,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5178,12 +5178,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5195,29 +5195,29 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5229,12 +5229,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5246,29 +5246,29 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5280,29 +5280,29 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5314,12 +5314,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5331,12 +5331,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5348,12 +5348,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5365,12 +5365,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5382,12 +5382,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5399,12 +5399,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5416,29 +5416,29 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5450,29 +5450,29 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5484,12 +5484,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5501,29 +5501,29 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5535,12 +5535,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5557,58 +5557,58 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5620,12 +5620,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5637,29 +5637,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5671,29 +5671,29 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5705,12 +5705,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5722,12 +5722,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5739,12 +5739,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5756,12 +5756,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5773,12 +5773,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5790,29 +5790,29 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5824,12 +5824,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5841,29 +5841,29 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5875,12 +5875,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5892,29 +5892,29 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5926,29 +5926,29 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5960,29 +5960,29 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5994,12 +5994,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6011,29 +6011,29 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6045,46 +6045,46 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6096,63 +6096,63 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6164,12 +6164,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6181,12 +6181,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6198,46 +6198,46 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6249,29 +6249,29 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6283,12 +6283,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6300,29 +6300,29 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6334,46 +6334,46 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6385,12 +6385,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6402,12 +6402,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6419,12 +6419,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6436,12 +6436,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6453,12 +6453,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6470,29 +6470,29 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6504,12 +6504,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6521,12 +6521,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6538,12 +6538,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6555,12 +6555,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6572,12 +6572,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6589,12 +6589,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6606,12 +6606,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6623,46 +6623,46 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6674,12 +6674,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -6691,12 +6691,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6708,12 +6708,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6725,29 +6725,29 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6759,12 +6759,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6776,29 +6776,29 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6810,12 +6810,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6827,12 +6827,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6844,12 +6844,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6861,12 +6861,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6878,29 +6878,29 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6912,12 +6912,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6929,24 +6929,24 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6963,7 +6963,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6980,7 +6980,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6990,14 +6990,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7014,7 +7014,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7041,19 +7041,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -7065,12 +7065,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -7082,12 +7082,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -7099,12 +7099,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -7116,12 +7116,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -7133,12 +7133,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -7150,29 +7150,29 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7184,12 +7184,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -7201,12 +7201,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7218,29 +7218,29 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7252,12 +7252,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7269,12 +7269,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7286,12 +7286,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7303,12 +7303,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7320,12 +7320,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7337,12 +7337,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7354,12 +7354,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7371,12 +7371,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7388,12 +7388,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7405,12 +7405,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7422,12 +7422,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7439,12 +7439,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7456,12 +7456,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7473,12 +7473,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7490,12 +7490,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7507,12 +7507,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7524,12 +7524,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7541,12 +7541,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7558,7 +7558,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7575,7 +7575,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7592,7 +7592,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7602,14 +7602,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7626,7 +7626,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7643,7 +7643,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7660,7 +7660,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7677,7 +7677,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7694,7 +7694,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7704,14 +7704,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7745,7 +7745,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -7755,14 +7755,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7813,7 +7813,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -7830,7 +7830,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -7847,7 +7847,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -7864,7 +7864,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7881,7 +7881,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7898,7 +7898,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7915,7 +7915,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7932,7 +7932,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7949,12 +7949,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7966,12 +7966,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7983,12 +7983,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8000,12 +8000,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8017,12 +8017,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8034,12 +8034,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8051,29 +8051,29 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8085,12 +8085,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8102,12 +8102,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8119,12 +8119,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8136,12 +8136,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8153,12 +8153,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8170,12 +8170,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8187,12 +8187,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8204,12 +8204,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8221,12 +8221,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8238,12 +8238,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8255,63 +8255,63 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -8323,12 +8323,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8340,29 +8340,29 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8374,46 +8374,46 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8425,12 +8425,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8442,12 +8442,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8459,7 +8459,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -8510,7 +8510,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -8520,14 +8520,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -8544,7 +8544,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -8554,14 +8554,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8571,36 +8571,36 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8612,29 +8612,29 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8646,63 +8646,63 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8714,80 +8714,80 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8799,63 +8799,63 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8867,63 +8867,63 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8935,29 +8935,29 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8969,12 +8969,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8986,63 +8986,63 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9054,29 +9054,29 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9088,29 +9088,29 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9122,12 +9122,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9139,12 +9139,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9156,12 +9156,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9173,646 +9173,136 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>BORGOSESIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>Masi Agricola S.p.A.</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
           <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>RT&amp;L S.P.A.</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Indel B S.p.A.</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>Stellantis N.V.</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>BASTOGI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>Triboo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>Vimi Fasteners S.p.A.</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>SIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>Svas Biosana S.p.A.</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>TELECOM ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>Casta Diva Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>Dedem S.p.A.</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Itway S.p.A.</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>CROWDFUNDME S.p.A.</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Autostrade Meridionali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Anima Holding S.p.A.</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>SIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9827,608 +9317,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BANCA IFIS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0003188064</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>22.3799991607666</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>4.11081338024718</v>
-      </c>
-      <c r="I2" t="n">
-        <v>63</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0004776628</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-04-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>16.72999954223633</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>3.885236209116557</v>
-      </c>
-      <c r="I3" t="n">
-        <v>35</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CALTAGIRONE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0003127930</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>9.159999847412109</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>3.275109224862664</v>
-      </c>
-      <c r="I4" t="n">
-        <v>63</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CEMBRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IT0001128047</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>61.90000152587891</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3.327948221679386</v>
-      </c>
-      <c r="I5" t="n">
-        <v>63</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IT0003121677</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>14.4399995803833</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>5.193905968105934</v>
-      </c>
-      <c r="I6" t="n">
-        <v>63</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DE' LONGHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IT0003115950</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>34.56000137329102</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>2.459490643009363</v>
-      </c>
-      <c r="I7" t="n">
-        <v>63</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>EMAK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>IT0001237053</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.878000020980835</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>3.416856410377562</v>
-      </c>
-      <c r="I8" t="n">
-        <v>77</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EQUITA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IT0005312027</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>5.489999771118164</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>3.64298740142325</v>
-      </c>
-      <c r="I9" t="n">
-        <v>63</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EQUITA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>IT0005312027</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5.489999771118164</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>3.64298740142325</v>
-      </c>
-      <c r="I10" t="n">
-        <v>245</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>IT0005107492</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>37.54999923706055</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1.251664472834733</v>
-      </c>
-      <c r="I11" t="n">
-        <v>49</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MARR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IT0003428445</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>7.920000076293945</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>5.934343377177466</v>
-      </c>
-      <c r="I12" t="n">
-        <v>63</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Orsero S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>IT0005138703</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>16.63999938964844</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>3.004807802523386</v>
-      </c>
-      <c r="I13" t="n">
-        <v>56</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>IT0001454435</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>30.79999923706055</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1.136363664512229</v>
-      </c>
-      <c r="I14" t="n">
-        <v>63</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10439,401 +9330,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Anima Holding S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Autostrade Meridionali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CIRCLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CROWDFUNDME S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Casta Diva Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Dedem S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EMAK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Itway S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Simone S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Annual Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Svas Biosana S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TELECOM ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>